--- a/powerapps/kolo-fortuny/sharepoint/Team_Members.xlsx
+++ b/powerapps/kolo-fortuny/sharepoint/Team_Members.xlsx
@@ -39,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7A1218"/>
+        <fgColor rgb="FFA32127"/>
       </patternFill>
     </fill>
   </fills>
@@ -441,140 +441,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Romanowski Piotr</t>
+          <t>Barszczyński Fabian</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Klein Ewa</t>
+          <t>Bigosiewicz Norbert</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gwiazda Marcin</t>
+          <t>Chałkowski Zbigniew</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adamczyk Natalia</t>
+          <t>Grzybowiecki Patryk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Borowiec Tomasz</t>
+          <t>Kluskowska Gabriela</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cieślak Magdalena</t>
+          <t>Kompotowski Bartosz</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dąbrowski Rafał</t>
+          <t>Makowiecki Damian</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Fijałkowska Iwona</t>
+          <t>Naleśnikowska Iwona</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Grabowski Michał</t>
+          <t>Ogórecki Jakub</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Herman Alicja</t>
+          <t>Piernikowski Leon</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jankowski Paweł</t>
+          <t>Pierogowska Anna</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kowalczyk Dorota</t>
+          <t>Placuszek Weronika</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lewandowska Karolina</t>
+          <t>Pyzowska Renata</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maj Sebastian</t>
+          <t>Rogalik Emilia</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nowicki Adam</t>
+          <t>Sernikowska Marta</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ostrowska Joanna</t>
+          <t>Serowacki Henryk</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pawlak Krzysztof</t>
+          <t>Śliwkowska Olga</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rutkowska Beata</t>
+          <t>Truskawiecka Kamila</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sikora Damian</t>
+          <t>Zapiekanko Sebastian</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wójcik Anna</t>
+          <t>Żurkiewicz Celina</t>
         </is>
       </c>
     </row>
